--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488191_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488191_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1116</v>
+        <v>6.3862</v>
       </c>
       <c r="E2" t="n">
-        <v>2.781</v>
+        <v>3.1295</v>
       </c>
       <c r="F2" t="n">
-        <v>3.3305</v>
+        <v>3.2567</v>
       </c>
       <c r="G2" t="n">
         <v>2.0221</v>
@@ -610,13 +610,13 @@
         <v>2.0382</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4832</v>
+        <v>-0.2086</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8754</v>
+        <v>-0.5269</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3922</v>
+        <v>0.3183</v>
       </c>
       <c r="V2" t="n">
         <v>3.461</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1162</v>
+        <v>4.299</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6399</v>
+        <v>2.4781</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4763</v>
+        <v>1.821</v>
       </c>
       <c r="G3" t="n">
         <v>3.2454</v>
@@ -688,13 +688,13 @@
         <v>2.7793</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.3532</v>
+        <v>-0.1704</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.3132</v>
+        <v>-0.475</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0401</v>
+        <v>0.3046</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6289</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5878</v>
+        <v>1.5412</v>
       </c>
       <c r="E4" t="n">
-        <v>3.5643</v>
+        <v>2.4439</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9765</v>
+        <v>-0.9026999999999999</v>
       </c>
       <c r="G4" t="n">
         <v>1.1874</v>
@@ -766,13 +766,13 @@
         <v>2.4087</v>
       </c>
       <c r="S4" t="n">
-        <v>1.789</v>
+        <v>0.7423999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4624</v>
+        <v>0.342</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3265</v>
+        <v>0.4004</v>
       </c>
       <c r="V4" t="n">
         <v>-0.9444</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2268</v>
+        <v>0.41</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.3433</v>
+        <v>-0.7557</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1165</v>
+        <v>1.1657</v>
       </c>
       <c r="G6" t="n">
         <v>1.5984</v>
@@ -922,13 +922,13 @@
         <v>2.4087</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.86</v>
+        <v>-0.2232</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.3132</v>
+        <v>-0.7256</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4531</v>
+        <v>0.5024</v>
       </c>
       <c r="V6" t="n">
         <v>1.2583</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2779</v>
+        <v>-0.1258</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.4067</v>
+        <v>-1.1561</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1288</v>
+        <v>1.0303</v>
       </c>
       <c r="G7" t="n">
         <v>-0.3975</v>
@@ -1000,13 +1000,13 @@
         <v>1.4823</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4902</v>
+        <v>0.6423</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1131</v>
+        <v>0.1374</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6032999999999999</v>
+        <v>0.5049</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3934</v>
+        <v>-1.5105</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.8458</v>
+        <v>-2.889</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4524</v>
+        <v>1.3785</v>
       </c>
       <c r="G8" t="n">
         <v>0.9345</v>
@@ -1078,13 +1078,13 @@
         <v>2.4087</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.104</v>
+        <v>-0.221</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7697000000000001</v>
+        <v>-0.8129</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6657999999999999</v>
+        <v>0.5919</v>
       </c>
       <c r="V8" t="n">
         <v>-0.0005</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.686</v>
+        <v>-1.7828</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9121</v>
+        <v>-1.2058</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.774</v>
+        <v>-0.577</v>
       </c>
       <c r="G9" t="n">
         <v>-2.198</v>
@@ -1156,13 +1156,13 @@
         <v>0.9264</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1</v>
+        <v>-0.1968</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1604</v>
+        <v>-0.1334</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2604</v>
+        <v>-0.0634</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3144</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.6327</v>
+        <v>-4.805</v>
       </c>
       <c r="E10" t="n">
         <v>-4.4461</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1866</v>
+        <v>-0.3589</v>
       </c>
       <c r="G10" t="n">
         <v>-4.6483</v>
@@ -1234,13 +1234,13 @@
         <v>1.4823</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3862</v>
+        <v>0.2139</v>
       </c>
       <c r="T10" t="n">
         <v>-0.1679</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5541</v>
+        <v>0.3818</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.58</v>
+        <v>-7.12</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.9933</v>
+        <v>-7.2871</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4133</v>
+        <v>0.1671</v>
       </c>
       <c r="G11" t="n">
         <v>-2.803</v>
@@ -1312,13 +1312,13 @@
         <v>1.6676</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4464</v>
+        <v>-0.0936</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2226</v>
+        <v>-0.5164</v>
       </c>
       <c r="U11" t="n">
-        <v>0.669</v>
+        <v>0.4228</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2589</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.037099999999999</v>
+        <v>-1.763599999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-9.018000000000001</v>
+        <v>-8.744199999999999</v>
       </c>
       <c r="F12" t="n">
         <v>6.980699999999999</v>
@@ -1390,13 +1390,13 @@
         <v>17.6022</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2113999999999999</v>
+        <v>0.4849999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.1523</v>
+        <v>-2.8787</v>
       </c>
       <c r="U12" t="n">
-        <v>3.3635</v>
+        <v>3.3637</v>
       </c>
       <c r="V12" t="n">
         <v>1.5722</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ TORRERO</t>
+          <t>A. VICENTE FERNANDEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.7232</v>
+        <v>3.4897</v>
       </c>
       <c r="E13" t="n">
-        <v>2.3657</v>
+        <v>0.8976</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3576</v>
+        <v>2.5921</v>
       </c>
       <c r="G13" t="n">
-        <v>1.0981</v>
+        <v>1.7881</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9737</v>
+        <v>-0.2362</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1244</v>
+        <v>2.0243</v>
       </c>
       <c r="J13" t="n">
-        <v>0.964</v>
+        <v>3.1362</v>
       </c>
       <c r="K13" t="n">
-        <v>0.9011</v>
+        <v>-0.0476</v>
       </c>
       <c r="L13" t="n">
-        <v>0.06279999999999999</v>
+        <v>3.1839</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1342</v>
+        <v>-1.3481</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0726</v>
+        <v>-0.1885</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0616</v>
+        <v>-1.1596</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9264</v>
+        <v>0.7411</v>
       </c>
       <c r="Q13" t="n">
         <v>-1.8529</v>
       </c>
       <c r="R13" t="n">
-        <v>2.7793</v>
+        <v>2.594</v>
       </c>
       <c r="S13" t="n">
-        <v>2.6425</v>
+        <v>0.3305</v>
       </c>
       <c r="T13" t="n">
-        <v>1.6813</v>
+        <v>-0.3858</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9612000000000001</v>
+        <v>0.7163</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.9439</v>
+        <v>0.63</v>
       </c>
       <c r="W13" t="n">
-        <v>1.5733</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.5172</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B. VIDAL</t>
+          <t>J. LATORRE SANCHEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.1031</v>
+        <v>2.9212</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8047</v>
+        <v>1.254</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2984</v>
+        <v>1.6672</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.0537</v>
+        <v>2.1009</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.3579</v>
+        <v>2.3665</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3043</v>
+        <v>-0.2657</v>
       </c>
       <c r="J14" t="n">
-        <v>0.431</v>
+        <v>3.4085</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.357</v>
+        <v>3.1905</v>
       </c>
       <c r="L14" t="n">
-        <v>0.788</v>
+        <v>0.218</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.4847</v>
+        <v>-1.3077</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.001</v>
+        <v>-0.824</v>
       </c>
       <c r="O14" t="n">
         <v>-0.4837</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.4823</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.7793</v>
+        <v>-1.8529</v>
       </c>
       <c r="R14" t="n">
-        <v>2.7793</v>
+        <v>3.3352</v>
       </c>
       <c r="S14" t="n">
-        <v>1.6385</v>
+        <v>-0.3476</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3209</v>
+        <v>-0.6162</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3176</v>
+        <v>0.2686</v>
       </c>
       <c r="V14" t="n">
-        <v>2.5183</v>
+        <v>-0.3144</v>
       </c>
       <c r="W14" t="n">
-        <v>2.8321</v>
+        <v>0.3144</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.3139</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. VICENTE FERNANDEZ</t>
+          <t>B. VIDAL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.8277</v>
+        <v>2.1697</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4079</v>
+        <v>0.413</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4198</v>
+        <v>1.7567</v>
       </c>
       <c r="G15" t="n">
-        <v>1.7881</v>
+        <v>-1.0537</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2362</v>
+        <v>-1.3579</v>
       </c>
       <c r="I15" t="n">
-        <v>2.0243</v>
+        <v>0.3043</v>
       </c>
       <c r="J15" t="n">
-        <v>3.1362</v>
+        <v>0.431</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.0476</v>
+        <v>-0.357</v>
       </c>
       <c r="L15" t="n">
-        <v>3.1839</v>
+        <v>0.788</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.3481</v>
+        <v>-1.4847</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1885</v>
+        <v>-1.001</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.1596</v>
+        <v>-0.4837</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7411</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.8529</v>
+        <v>-2.7793</v>
       </c>
       <c r="R15" t="n">
-        <v>2.594</v>
+        <v>2.7793</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3315</v>
+        <v>0.7050999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8754</v>
+        <v>-0.0709</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5439000000000001</v>
+        <v>0.7759</v>
       </c>
       <c r="V15" t="n">
-        <v>0.63</v>
+        <v>2.5183</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.8321</v>
       </c>
       <c r="X15" t="n">
-        <v>0.63</v>
+        <v>-0.3139</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. LATORRE SANCHEZ</t>
+          <t>A. RODRIGUEZ TORRERO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2351</v>
+        <v>2.1312</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6664</v>
+        <v>0.8967000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5687</v>
+        <v>1.2344</v>
       </c>
       <c r="G16" t="n">
-        <v>2.1009</v>
+        <v>1.0981</v>
       </c>
       <c r="H16" t="n">
-        <v>2.3665</v>
+        <v>0.9737</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2657</v>
+        <v>0.1244</v>
       </c>
       <c r="J16" t="n">
-        <v>3.4085</v>
+        <v>0.964</v>
       </c>
       <c r="K16" t="n">
-        <v>3.1905</v>
+        <v>0.9011</v>
       </c>
       <c r="L16" t="n">
-        <v>0.218</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.3077</v>
+        <v>0.1342</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.824</v>
+        <v>0.0726</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4837</v>
+        <v>0.0616</v>
       </c>
       <c r="P16" t="n">
-        <v>1.4823</v>
+        <v>0.9264</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.8529</v>
       </c>
       <c r="R16" t="n">
-        <v>3.3352</v>
+        <v>2.7793</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0336</v>
+        <v>1.0505</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.2037</v>
+        <v>0.2124</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1701</v>
+        <v>0.8381</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.3144</v>
+        <v>-0.9439</v>
       </c>
       <c r="W16" t="n">
-        <v>0.3144</v>
+        <v>1.5733</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6289</v>
+        <v>-2.5172</v>
       </c>
     </row>
     <row r="17">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1313</v>
+        <v>0.7452</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.5758</v>
+        <v>-2.2821</v>
       </c>
       <c r="F18" t="n">
-        <v>2.7071</v>
+        <v>3.0272</v>
       </c>
       <c r="G18" t="n">
         <v>-0.5648</v>
@@ -1858,13 +1858,13 @@
         <v>2.4087</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5066000000000001</v>
+        <v>0.1073</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6566</v>
+        <v>-0.3628</v>
       </c>
       <c r="U18" t="n">
-        <v>0.15</v>
+        <v>0.47</v>
       </c>
       <c r="V18" t="n">
         <v>1.5733</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5676</v>
+        <v>0.1196</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0091</v>
+        <v>-0.6173999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4416</v>
+        <v>0.737</v>
       </c>
       <c r="G19" t="n">
         <v>0.6208</v>
@@ -1936,13 +1936,13 @@
         <v>2.2234</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.5589</v>
+        <v>-0.8717</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0396</v>
+        <v>-0.6479</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5193</v>
+        <v>-0.2239</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3839</v>
+        <v>-1.2619</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4556</v>
+        <v>-1.2597</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0717</v>
+        <v>-0.0022</v>
       </c>
       <c r="G20" t="n">
         <v>0.3371</v>
@@ -2014,13 +2014,13 @@
         <v>2.2234</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8327</v>
+        <v>-0.7107</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.149</v>
+        <v>-0.9532</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3163</v>
+        <v>0.2425</v>
       </c>
       <c r="V20" t="n">
         <v>-1.2589</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. TARRES HERNANDEZ</t>
+          <t>A. FERNANDEZ AMESTOY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5566</v>
+        <v>-2.3988</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.7791</v>
+        <v>-1.0044</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2225</v>
+        <v>-1.3944</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.9561</v>
+        <v>0.3505</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.5829</v>
+        <v>0.3505</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3732</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.1584</v>
+        <v>0.0429</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.1999</v>
+        <v>0.0429</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0415</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.7977</v>
+        <v>0.3076</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.383</v>
+        <v>0.3076</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4147</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9264</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9264</v>
+        <v>0.7411</v>
       </c>
       <c r="S21" t="n">
-        <v>0.473</v>
+        <v>-0.0463</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3793</v>
+        <v>-0.1209</v>
       </c>
       <c r="U21" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.0746</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-2.5177</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-2.5177</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. FERNANDEZ AMESTOY</t>
+          <t>G. TARRES HERNANDEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6198</v>
+        <v>-3.0222</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1024</v>
+        <v>-3.1708</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.5175</v>
+        <v>0.1486</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3505</v>
+        <v>-3.9561</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3505</v>
+        <v>-3.5829</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>-0.3732</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0429</v>
+        <v>-3.1584</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0429</v>
+        <v>-3.1999</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>0.0415</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3076</v>
+        <v>-0.7977</v>
       </c>
       <c r="N22" t="n">
-        <v>0.3076</v>
+        <v>-0.383</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>-0.4147</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.1853</v>
+        <v>0.9264</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7411</v>
+        <v>0.9264</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2674</v>
+        <v>0.0075</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2189</v>
+        <v>-0.0124</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0485</v>
+        <v>0.0199</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.5177</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.5177</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.8216</v>
+        <v>-3.8227</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.2696</v>
+        <v>-3.0737</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.552</v>
+        <v>-0.749</v>
       </c>
       <c r="G23" t="n">
         <v>-1.5721</v>
@@ -2248,13 +2248,13 @@
         <v>1.297</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4347</v>
+        <v>-0.4359</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6019</v>
+        <v>-0.406</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1671</v>
+        <v>-0.0299</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2589</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>2.037100000000001</v>
+        <v>2.037199999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.980700000000001</v>
+        <v>-6.980599999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>9.017900000000001</v>
+        <v>9.017599999999998</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1149999999999998</v>
+        <v>0.115</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.0001000000000004331</v>
+        <v>-0.000100000000000211</v>
       </c>
       <c r="I24" t="n">
         <v>0.1150000000000002</v>
@@ -2302,7 +2302,7 @@
         <v>7.377599999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>4.729000000000001</v>
+        <v>4.729000000000002</v>
       </c>
       <c r="L24" t="n">
         <v>2.648499999999999</v>
@@ -2326,13 +2326,13 @@
         <v>21.3078</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2113999999999995</v>
+        <v>-0.2113000000000004</v>
       </c>
       <c r="T24" t="n">
-        <v>-3.3636</v>
+        <v>-3.3637</v>
       </c>
       <c r="U24" t="n">
-        <v>3.1522</v>
+        <v>3.152099999999999</v>
       </c>
       <c r="V24" t="n">
         <v>-1.5722</v>
